--- a/documentation/top_päiväkirja_kevät_2026.xlsx
+++ b/documentation/top_päiväkirja_kevät_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eerikki.maula\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="699" documentId="13_ncr:1_{29FB6FE2-3BAC-4CB8-8820-8FFAC7EC2DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{227EA0CA-5770-4B40-8383-AE01BA158E1E}"/>
+  <xr:revisionPtr revIDLastSave="704" documentId="13_ncr:1_{29FB6FE2-3BAC-4CB8-8820-8FFAC7EC2DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E7A5678-9DD7-4B8C-A8F5-4D804C2C2E8C}"/>
   <bookViews>
     <workbookView xWindow="-27630" yWindow="1335" windowWidth="19230" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="107">
   <si>
     <t>Opiskelija</t>
   </si>
@@ -376,6 +376,12 @@
     <t>Kuinka yhdistää UI (liukusäätimet) ja pelilogiikka (ääni).
 Kuinka näyttää ja päivittää reaaliaikaisia arvoja käyttöliittymässä.
 Kuinka suunnitella yhtenäinen audiojärjestelmä koko peliin.</t>
+  </si>
+  <si>
+    <t>Kokous. Pelin julkaisu</t>
+  </si>
+  <si>
+    <t>Kuinka saada tietoja db.json tiedostosta WebGL-versioon (UnityWebRequest); kuinka julkaista pelin</t>
   </si>
   <si>
     <t>Opiskelija nimi</t>
@@ -667,7 +673,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -780,6 +786,18 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -788,27 +806,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1105,10 +1102,10 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="40"/>
+      <c r="C1" s="44"/>
       <c r="E1" t="s">
         <v>2</v>
       </c>
@@ -1117,10 +1114,10 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="41"/>
+      <c r="C2" s="45"/>
       <c r="E2" t="s">
         <v>5</v>
       </c>
@@ -1455,7 +1452,7 @@
       <c r="C20" s="15">
         <v>6</v>
       </c>
-      <c r="D20" s="43" t="s">
+      <c r="D20" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E20" s="6" t="s">
@@ -1475,7 +1472,7 @@
       <c r="C21" s="18">
         <v>6</v>
       </c>
-      <c r="D21" s="44" t="s">
+      <c r="D21" s="7" t="s">
         <v>42</v>
       </c>
       <c r="E21" s="7" t="s">
@@ -1495,7 +1492,7 @@
       <c r="C22" s="18">
         <v>6</v>
       </c>
-      <c r="D22" s="44" t="s">
+      <c r="D22" s="7" t="s">
         <v>44</v>
       </c>
       <c r="E22" s="7" t="s">
@@ -1515,7 +1512,7 @@
       <c r="C23" s="18">
         <v>6</v>
       </c>
-      <c r="D23" s="44" t="s">
+      <c r="D23" s="7" t="s">
         <v>46</v>
       </c>
       <c r="E23" s="7" t="s">
@@ -1555,7 +1552,7 @@
       <c r="C25" s="15">
         <v>6</v>
       </c>
-      <c r="D25" s="43" t="s">
+      <c r="D25" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E25" s="6" t="s">
@@ -1575,7 +1572,7 @@
       <c r="C26" s="18">
         <v>6</v>
       </c>
-      <c r="D26" s="44" t="s">
+      <c r="D26" s="7" t="s">
         <v>52</v>
       </c>
       <c r="E26" s="7" t="s">
@@ -1595,7 +1592,7 @@
       <c r="C27" s="18">
         <v>6</v>
       </c>
-      <c r="D27" s="44" t="s">
+      <c r="D27" s="7" t="s">
         <v>54</v>
       </c>
       <c r="E27" s="7" t="s">
@@ -1615,7 +1612,7 @@
       <c r="C28" s="18">
         <v>6</v>
       </c>
-      <c r="D28" s="44" t="s">
+      <c r="D28" s="7" t="s">
         <v>56</v>
       </c>
       <c r="E28" s="7" t="s">
@@ -1635,7 +1632,7 @@
       <c r="C29" s="21">
         <v>6</v>
       </c>
-      <c r="D29" s="45" t="s">
+      <c r="D29" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E29" s="8" t="s">
@@ -1655,7 +1652,7 @@
       <c r="C30" s="26">
         <v>6</v>
       </c>
-      <c r="D30" s="43" t="s">
+      <c r="D30" s="6" t="s">
         <v>60</v>
       </c>
       <c r="E30" s="11" t="s">
@@ -1675,7 +1672,7 @@
       <c r="C31" s="29">
         <v>6</v>
       </c>
-      <c r="D31" s="44" t="s">
+      <c r="D31" s="7" t="s">
         <v>62</v>
       </c>
       <c r="E31" s="12" t="s">
@@ -1695,7 +1692,7 @@
       <c r="C32" s="29">
         <v>6</v>
       </c>
-      <c r="D32" s="44" t="s">
+      <c r="D32" s="7" t="s">
         <v>64</v>
       </c>
       <c r="E32" s="12" t="s">
@@ -1715,7 +1712,7 @@
       <c r="C33" s="29">
         <v>6</v>
       </c>
-      <c r="D33" s="44" t="s">
+      <c r="D33" s="7" t="s">
         <v>66</v>
       </c>
       <c r="E33" s="12" t="s">
@@ -1735,7 +1732,7 @@
       <c r="C34" s="32">
         <v>6</v>
       </c>
-      <c r="D34" s="45" t="s">
+      <c r="D34" s="8" t="s">
         <v>68</v>
       </c>
       <c r="E34" s="13" t="s">
@@ -1821,7 +1818,7 @@
       <c r="C40" s="15">
         <v>6</v>
       </c>
-      <c r="D40" s="47" t="s">
+      <c r="D40" s="41" t="s">
         <v>72</v>
       </c>
       <c r="E40" s="6"/>
@@ -1839,7 +1836,7 @@
       <c r="C41" s="23">
         <v>6</v>
       </c>
-      <c r="D41" s="48" t="s">
+      <c r="D41" s="42" t="s">
         <v>73</v>
       </c>
       <c r="E41" s="24" t="s">
@@ -1859,7 +1856,7 @@
       <c r="C42" s="23">
         <v>6</v>
       </c>
-      <c r="D42" s="49" t="s">
+      <c r="D42" s="43" t="s">
         <v>66</v>
       </c>
       <c r="E42" s="12" t="s">
@@ -1879,7 +1876,7 @@
       <c r="C43" s="23">
         <v>6</v>
       </c>
-      <c r="D43" s="48" t="s">
+      <c r="D43" s="42" t="s">
         <v>75</v>
       </c>
       <c r="E43" s="24" t="s">
@@ -1899,7 +1896,7 @@
       <c r="C44" s="21">
         <v>6</v>
       </c>
-      <c r="D44" s="46" t="s">
+      <c r="D44" s="40" t="s">
         <v>77</v>
       </c>
       <c r="E44" s="8" t="s">
@@ -1919,7 +1916,7 @@
       <c r="C45" s="15">
         <v>2</v>
       </c>
-      <c r="D45" s="43" t="s">
+      <c r="D45" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E45" s="6"/>
@@ -1937,7 +1934,7 @@
       <c r="C46" s="18">
         <v>6</v>
       </c>
-      <c r="D46" s="44" t="s">
+      <c r="D46" s="7" t="s">
         <v>80</v>
       </c>
       <c r="E46" s="7" t="s">
@@ -1957,7 +1954,7 @@
       <c r="C47" s="18">
         <v>6</v>
       </c>
-      <c r="D47" s="44" t="s">
+      <c r="D47" s="7" t="s">
         <v>82</v>
       </c>
       <c r="E47" s="7" t="s">
@@ -1977,7 +1974,7 @@
       <c r="C48" s="18">
         <v>6</v>
       </c>
-      <c r="D48" s="44" t="s">
+      <c r="D48" s="7" t="s">
         <v>84</v>
       </c>
       <c r="E48" s="7" t="s">
@@ -1997,7 +1994,7 @@
       <c r="C49" s="21">
         <v>6</v>
       </c>
-      <c r="D49" s="45" t="s">
+      <c r="D49" s="8" t="s">
         <v>86</v>
       </c>
       <c r="E49" s="8" t="s">
@@ -2017,7 +2014,7 @@
       <c r="C50" s="15">
         <v>6</v>
       </c>
-      <c r="D50" s="43" t="s">
+      <c r="D50" s="6" t="s">
         <v>88</v>
       </c>
       <c r="E50" s="6" t="s">
@@ -2037,7 +2034,7 @@
       <c r="C51" s="18">
         <v>6</v>
       </c>
-      <c r="D51" s="44" t="s">
+      <c r="D51" s="7" t="s">
         <v>90</v>
       </c>
       <c r="E51" s="7" t="s">
@@ -2057,7 +2054,7 @@
       <c r="C52" s="18">
         <v>6</v>
       </c>
-      <c r="D52" s="44" t="s">
+      <c r="D52" s="7" t="s">
         <v>92</v>
       </c>
       <c r="E52" s="7" t="s">
@@ -2077,7 +2074,7 @@
       <c r="C53" s="18">
         <v>6</v>
       </c>
-      <c r="D53" s="44" t="s">
+      <c r="D53" s="7" t="s">
         <v>92</v>
       </c>
       <c r="E53" s="7" t="s">
@@ -2097,7 +2094,7 @@
       <c r="C54" s="21">
         <v>6</v>
       </c>
-      <c r="D54" s="45" t="s">
+      <c r="D54" s="8" t="s">
         <v>93</v>
       </c>
       <c r="E54" s="8" t="s">
@@ -2117,7 +2114,7 @@
       <c r="C55" s="15">
         <v>6</v>
       </c>
-      <c r="D55" s="43" t="s">
+      <c r="D55" s="6" t="s">
         <v>95</v>
       </c>
       <c r="E55" s="6" t="s">
@@ -2137,7 +2134,7 @@
       <c r="C56" s="18">
         <v>6</v>
       </c>
-      <c r="D56" s="44" t="s">
+      <c r="D56" s="7" t="s">
         <v>97</v>
       </c>
       <c r="E56" s="7" t="s">
@@ -2157,7 +2154,7 @@
       <c r="C57" s="18">
         <v>4</v>
       </c>
-      <c r="D57" s="44" t="s">
+      <c r="D57" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E57" s="7" t="s">
@@ -2177,7 +2174,7 @@
       <c r="C58" s="18">
         <v>6</v>
       </c>
-      <c r="D58" s="44" t="s">
+      <c r="D58" s="7" t="s">
         <v>101</v>
       </c>
       <c r="E58" s="7" t="s">
@@ -2187,7 +2184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15">
+    <row r="59" spans="1:6" ht="60.75">
       <c r="A59" s="20">
         <v>46108</v>
       </c>
@@ -2198,9 +2195,11 @@
         <v>6</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E59" s="8"/>
+        <v>103</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>104</v>
+      </c>
       <c r="F59" s="22">
         <v>3</v>
       </c>
@@ -2238,12 +2237,12 @@
       <c r="D64" s="1"/>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="B65" s="42"/>
+      <c r="A65" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="B65" s="46"/>
       <c r="D65" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15"/>
@@ -2296,14 +2295,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="94885e40-5ce3-4968-98dc-e37accdc5885">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="21f2f96f-3940-4dcd-b8d7-2051c5acc894" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2530,16 +2527,18 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="94885e40-5ce3-4968-98dc-e37accdc5885">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="21f2f96f-3940-4dcd-b8d7-2051c5acc894" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14F0D827-B951-4FD8-9FEE-A35AFC155082}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEA345B0-F36E-4CF8-BDEB-6E48E486E075}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2547,5 +2546,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEA345B0-F36E-4CF8-BDEB-6E48E486E075}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14F0D827-B951-4FD8-9FEE-A35AFC155082}"/>
 </file>